--- a/data/1455推广_开发任务跟踪模板_V1.0.xlsx
+++ b/data/1455推广_开发任务跟踪模板_V1.0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhahuang\Documents\Customer-Data\国电投\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE15AABC-36C3-4FDE-B824-BAFEF6E83022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9D2F3FA-26F8-454D-9040-557E8C01ED27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="任务模板" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="196">
   <si>
     <t>基础信息</t>
   </si>
@@ -675,6 +675,38 @@
   </si>
   <si>
     <t>所有 JAVA/SAP 任务统一填写此表。</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>FS附件</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TS附件</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统测试报告附件</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>集成测试报告附件</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>回归测试报告附件</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>附件</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能说明书附件</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>技术说明书附件</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -778,7 +810,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -835,6 +867,12 @@
         <fgColor rgb="FFFAFAFA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -874,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -956,6 +994,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -976,6 +1020,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1278,7 +1325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B119C34C-741A-4B92-AD94-0A4F8BDC0608}">
-  <dimension ref="A1:AJ96"/>
+  <dimension ref="A1:AO96"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1308,7 +1355,7 @@
     <col min="34" max="34" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="16.5">
+    <row r="1" spans="1:41" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>114</v>
       </c>
@@ -1417,8 +1464,23 @@
       <c r="AJ1" s="26" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" ht="16.5">
+      <c r="AK1" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL1" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM1" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="AN1" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AO1" s="30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="16.5">
       <c r="A2" s="8"/>
       <c r="B2" s="8"/>
       <c r="C2" s="7"/>
@@ -1454,7 +1516,7 @@
       <c r="AG2" s="7"/>
       <c r="AH2" s="7"/>
     </row>
-    <row r="3" spans="1:36" ht="16.5">
+    <row r="3" spans="1:41" ht="16.5">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="5"/>
@@ -1490,7 +1552,7 @@
       <c r="AG3" s="5"/>
       <c r="AH3" s="5"/>
     </row>
-    <row r="4" spans="1:36" ht="16.5">
+    <row r="4" spans="1:41" ht="16.5">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="7"/>
@@ -1526,7 +1588,7 @@
       <c r="AG4" s="7"/>
       <c r="AH4" s="7"/>
     </row>
-    <row r="5" spans="1:36" ht="16.5">
+    <row r="5" spans="1:41" ht="16.5">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="5"/>
@@ -1562,7 +1624,7 @@
       <c r="AG5" s="5"/>
       <c r="AH5" s="5"/>
     </row>
-    <row r="6" spans="1:36" ht="16.5">
+    <row r="6" spans="1:41" ht="16.5">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="7"/>
@@ -1600,7 +1662,7 @@
       <c r="AG6" s="7"/>
       <c r="AH6" s="7"/>
     </row>
-    <row r="7" spans="1:36" ht="16.5">
+    <row r="7" spans="1:41" ht="16.5">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="5"/>
@@ -1636,7 +1698,7 @@
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
     </row>
-    <row r="8" spans="1:36" ht="16.5">
+    <row r="8" spans="1:41" ht="16.5">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="7"/>
@@ -1671,7 +1733,7 @@
       <c r="AG8" s="7"/>
       <c r="AH8" s="7"/>
     </row>
-    <row r="9" spans="1:36" ht="16.5">
+    <row r="9" spans="1:41" ht="16.5">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -1707,7 +1769,7 @@
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
     </row>
-    <row r="10" spans="1:36" ht="16.5">
+    <row r="10" spans="1:41" ht="16.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="7"/>
@@ -1742,7 +1804,7 @@
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
     </row>
-    <row r="11" spans="1:36" ht="16.5">
+    <row r="11" spans="1:41" ht="16.5">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
@@ -1778,7 +1840,7 @@
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
     </row>
-    <row r="12" spans="1:36" ht="16.5">
+    <row r="12" spans="1:41" ht="16.5">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="7"/>
@@ -1814,7 +1876,7 @@
       <c r="AG12" s="7"/>
       <c r="AH12" s="7"/>
     </row>
-    <row r="13" spans="1:36" ht="16.5">
+    <row r="13" spans="1:41" ht="16.5">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
@@ -1850,7 +1912,7 @@
       <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
     </row>
-    <row r="14" spans="1:36" ht="16.5">
+    <row r="14" spans="1:41" ht="16.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="7"/>
@@ -1886,7 +1948,7 @@
       <c r="AG14" s="7"/>
       <c r="AH14" s="7"/>
     </row>
-    <row r="15" spans="1:36" ht="16.5">
+    <row r="15" spans="1:41" ht="16.5">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -1922,7 +1984,7 @@
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
     </row>
-    <row r="16" spans="1:36" ht="16.5">
+    <row r="16" spans="1:41" ht="16.5">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
@@ -4843,11 +4905,11 @@
     <dataValidation type="list" allowBlank="1" sqref="H19:H96 H9 H11:H17 H2:H7" xr:uid="{2BE9FB19-A61F-4064-B1D2-9C45BC18CD8E}">
       <formula1>"PO,报表,接口,增强,功能,H5,FIORI,直连,SAP-MM,SAP-FICO,MM,FICO,SD,PM,PP,PS,MDG,GRC,WMS,BPM,其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="AE2:AG1048576 R1 AE1:AG1 R2:R1048576" xr:uid="{AFA54FC4-C0CC-47A4-8F71-CB91CE296B28}"/>
-    <dataValidation type="list" allowBlank="1" sqref="U1 U2:U1048576" xr:uid="{3E9D64E4-9965-4A49-98C7-35F796DCF3B7}">
+    <dataValidation allowBlank="1" sqref="AE1:AG1048576 R1:R1048576 AM1:AO1" xr:uid="{AFA54FC4-C0CC-47A4-8F71-CB91CE296B28}"/>
+    <dataValidation type="list" allowBlank="1" sqref="U1:U1048576" xr:uid="{3E9D64E4-9965-4A49-98C7-35F796DCF3B7}">
       <formula1>"待处理,进行中,已完成,已取消"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" sqref="Z2:Z1048576 Z1" xr:uid="{FA0183D1-5FA9-47B4-A0BD-3B41CEBE4B72}">
+    <dataValidation type="custom" allowBlank="1" sqref="Z1:Z1048576" xr:uid="{FA0183D1-5FA9-47B4-A0BD-3B41CEBE4B72}">
       <formula1>"未开始,进行中,已完成,已取消,不适用"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G2:G96" xr:uid="{99B00E3A-D17B-4756-AFD8-C1E8ACD61DE6}">
@@ -4875,7 +4937,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D16AB764-EF4B-4874-8E82-0007BE5DCAF1}">
-  <dimension ref="A1:AK510"/>
+  <dimension ref="A1:AO510"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="47.875" customWidth="1"/>
@@ -4905,14 +4967,18 @@
     <col min="31" max="33" width="14" customWidth="1"/>
     <col min="34" max="34" width="20" customWidth="1"/>
     <col min="36" max="36" width="16.5" customWidth="1"/>
+    <col min="38" max="38" width="11.375" customWidth="1"/>
+    <col min="39" max="39" width="14.5" customWidth="1"/>
+    <col min="40" max="40" width="14.25" customWidth="1"/>
+    <col min="41" max="41" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="29" customFormat="1" ht="48.75" customHeight="1">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:41" s="31" customFormat="1" ht="48.75" customHeight="1">
+      <c r="A1" s="31" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="16.5">
+    <row r="2" spans="1:41" ht="16.5">
       <c r="A2" s="8"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -4921,48 +4987,48 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="30" t="s">
+      <c r="I2" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="32" t="s">
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="31"/>
-      <c r="P2" s="33" t="s">
+      <c r="O2" s="33"/>
+      <c r="P2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="34" t="s">
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="33"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="35" t="s">
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="33"/>
+      <c r="Y2" s="33"/>
+      <c r="Z2" s="33"/>
+      <c r="AA2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="35" t="s">
+      <c r="AB2" s="33"/>
+      <c r="AC2" s="33"/>
+      <c r="AD2" s="33"/>
+      <c r="AE2" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-    </row>
-    <row r="3" spans="1:37" ht="16.5">
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="37"/>
+      <c r="AJ2" s="37"/>
+    </row>
+    <row r="3" spans="1:41" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>114</v>
       </c>
@@ -5071,8 +5137,23 @@
       <c r="AJ3" s="26" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="4" spans="1:37">
+      <c r="AK3" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL3" s="29" t="s">
+        <v>189</v>
+      </c>
+      <c r="AM3" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="AN3" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="AO3" s="30" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41">
       <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
@@ -5181,8 +5262,23 @@
       <c r="AJ4" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:37" s="17" customFormat="1" ht="15" customHeight="1">
+      <c r="AK4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO4" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" s="17" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="15" t="s">
         <v>183</v>
       </c>
@@ -5223,7 +5319,7 @@
       <c r="AJ5" s="16"/>
       <c r="AK5" s="16"/>
     </row>
-    <row r="6" spans="1:37" ht="16.5">
+    <row r="6" spans="1:41" ht="16.5">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="7"/>
@@ -5259,7 +5355,7 @@
       <c r="AG6" s="7"/>
       <c r="AH6" s="7"/>
     </row>
-    <row r="7" spans="1:37" ht="16.5">
+    <row r="7" spans="1:41" ht="16.5">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="5"/>
@@ -5294,7 +5390,7 @@
       <c r="AG7" s="5"/>
       <c r="AH7" s="5"/>
     </row>
-    <row r="8" spans="1:37" ht="16.5">
+    <row r="8" spans="1:41" ht="16.5">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="7"/>
@@ -5330,7 +5426,7 @@
       <c r="AG8" s="7"/>
       <c r="AH8" s="7"/>
     </row>
-    <row r="9" spans="1:37" ht="16.5">
+    <row r="9" spans="1:41" ht="16.5">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="5"/>
@@ -5366,7 +5462,7 @@
       <c r="AG9" s="5"/>
       <c r="AH9" s="5"/>
     </row>
-    <row r="10" spans="1:37" ht="16.5">
+    <row r="10" spans="1:41" ht="16.5">
       <c r="A10" s="8"/>
       <c r="B10" s="8"/>
       <c r="C10" s="7"/>
@@ -5402,7 +5498,7 @@
       <c r="AG10" s="7"/>
       <c r="AH10" s="7"/>
     </row>
-    <row r="11" spans="1:37" ht="16.5">
+    <row r="11" spans="1:41" ht="16.5">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="5"/>
@@ -5438,7 +5534,7 @@
       <c r="AG11" s="5"/>
       <c r="AH11" s="5"/>
     </row>
-    <row r="12" spans="1:37" ht="16.5">
+    <row r="12" spans="1:41" ht="16.5">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="7"/>
@@ -5474,7 +5570,7 @@
       <c r="AG12" s="7"/>
       <c r="AH12" s="7"/>
     </row>
-    <row r="13" spans="1:37" ht="16.5">
+    <row r="13" spans="1:41" ht="16.5">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="5"/>
@@ -5510,7 +5606,7 @@
       <c r="AG13" s="5"/>
       <c r="AH13" s="5"/>
     </row>
-    <row r="14" spans="1:37" ht="16.5">
+    <row r="14" spans="1:41" ht="16.5">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="7"/>
@@ -5548,7 +5644,7 @@
       <c r="AG14" s="7"/>
       <c r="AH14" s="7"/>
     </row>
-    <row r="15" spans="1:37" ht="16.5">
+    <row r="15" spans="1:41" ht="16.5">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="5"/>
@@ -5584,7 +5680,7 @@
       <c r="AG15" s="5"/>
       <c r="AH15" s="5"/>
     </row>
-    <row r="16" spans="1:37" ht="16.5">
+    <row r="16" spans="1:41" ht="16.5">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="7"/>
@@ -10030,7 +10126,7 @@
     <dataValidation type="list" allowBlank="1" sqref="G6:G104 B2" xr:uid="{8A39FA1E-61F4-42F4-AFF7-D2AD70E6EE6A}">
       <formula1>"开发,集成,需求,功能,报表,优化,问题,接口,增强,测试,文档,其他"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" sqref="R3 AE3:AG3 AE6:AG1048576 R6 R8:R1048576" xr:uid="{0DA917DC-E29E-4A92-9B22-44576D414CF2}"/>
+    <dataValidation allowBlank="1" sqref="R3 AE3:AG3 AE6:AG1048576 R6 R8:R1048576 AM3:AO3" xr:uid="{0DA917DC-E29E-4A92-9B22-44576D414CF2}"/>
     <dataValidation type="list" allowBlank="1" sqref="H27:H104 H17 H19:H25 H6:H15 C2" xr:uid="{B8057452-624C-4249-8A84-E2BD15E22795}">
       <formula1>"PO,报表,接口,增强,功能,H5,FIORI,直连,SAP-MM,SAP-FICO,MM,FICO,SD,PM,PP,PS,MDG,GRC,WMS,BPM,其他"</formula1>
     </dataValidation>
@@ -10056,7 +10152,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -10067,13 +10163,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="3" spans="1:5" ht="16.5">
       <c r="A3" s="1" t="s">
@@ -10719,6 +10815,91 @@
       </c>
       <c r="E40" s="28" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16.5">
+      <c r="A41" s="7">
+        <v>38</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="16.5">
+      <c r="A42" s="7">
+        <v>39</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16.5">
+      <c r="A43" s="7">
+        <v>40</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E43" s="39" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16.5">
+      <c r="A44" s="7">
+        <v>41</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16.5">
+      <c r="A45" s="7">
+        <v>42</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -10742,12 +10923,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="3" spans="1:4" ht="16.5">
       <c r="A3" s="1" t="s">
